--- a/jogos_2024-10-23.xlsx
+++ b/jogos_2024-10-23.xlsx
@@ -1675,16 +1675,16 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
         <v>1</v>
@@ -1693,7 +1693,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="O10" t="n">
         <v>4</v>
@@ -1716,62 +1716,62 @@
         <v>1.91</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="S10" t="n">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="T10" t="n">
-        <v>3.65</v>
+        <v>3.84</v>
       </c>
       <c r="U10" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="V10" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W10" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="X10" t="n">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AA10" t="n">
         <v>4.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['79']</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>['55']</t>
+          <t>['38']</t>
         </is>
       </c>
       <c r="AG10" t="n">
         <v>1.48</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AI10" t="n">
         <v>2.5</v>
@@ -1804,25 +1804,25 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Otrant-Olympic</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
         <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.1</v>
+        <v>2.36</v>
       </c>
       <c r="M11" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="N11" t="n">
         <v>3</v>
       </c>
-      <c r="N11" t="n">
-        <v>2.2</v>
-      </c>
       <c r="O11" t="n">
+        <v>3</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AA11" t="n">
         <v>4</v>
       </c>
-      <c r="P11" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AB11" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.22</v>
+        <v>1.93</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.59</v>
+        <v>1.78</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>['79']</t>
+          <t>['9', '32']</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>['38']</t>
+          <t>['56']</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.48</v>
+        <v>1.31</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.27</v>
+        <v>1.45</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.5</v>
+        <v>1.83</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.8</v>
+        <v>2.38</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45588.45833333334</v>
@@ -2062,22 +2062,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Otrant-Olympic</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.36</v>
+        <v>2.8</v>
       </c>
       <c r="M13" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="N13" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="O13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="R13" t="n">
-        <v>1.51</v>
+        <v>1.59</v>
       </c>
       <c r="S13" t="n">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="T13" t="n">
-        <v>3.22</v>
+        <v>3.65</v>
       </c>
       <c r="U13" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="V13" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="W13" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="X13" t="n">
-        <v>2.75</v>
+        <v>2.37</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.21</v>
+        <v>2.47</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.59</v>
+        <v>1.48</v>
       </c>
       <c r="AA13" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.93</v>
+        <v>2.13</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.78</v>
+        <v>1.64</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>['9', '32']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>['56']</t>
+          <t>['55']</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.31</v>
+        <v>1.48</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.45</v>
+        <v>1.28</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.38</v>
+        <v>1.8</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45588.45833333334</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2467,7 +2467,7 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4.6</v>
+        <v>3.45</v>
       </c>
       <c r="M16" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="N16" t="n">
-        <v>1.55</v>
+        <v>1.94</v>
       </c>
       <c r="O16" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="P16" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q16" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q16" t="n">
-        <v>1.8</v>
-      </c>
       <c r="R16" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S16" t="n">
-        <v>3.5</v>
+        <v>3.46</v>
       </c>
       <c r="T16" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="U16" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="V16" t="n">
         <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X16" t="n">
-        <v>4.75</v>
+        <v>4.4</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="Z16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA16" t="n">
         <v>2.35</v>
       </c>
-      <c r="AA16" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AB16" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.7</v>
+        <v>1.48</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2538,20 +2538,20 @@
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>['19']</t>
+          <t>['77']</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>2.9</v>
+        <v>1.62</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.06</v>
+        <v>1.28</v>
       </c>
       <c r="AI16" t="n">
-        <v>4</v>
+        <v>2.38</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45588.5</v>
@@ -2568,33 +2568,33 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
         <v>1</v>
       </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.31</v>
+        <v>1.91</v>
       </c>
       <c r="M17" t="n">
-        <v>3.06</v>
+        <v>2.9</v>
       </c>
       <c r="N17" t="n">
-        <v>2.63</v>
+        <v>4.1</v>
       </c>
       <c r="O17" t="n">
-        <v>3.14</v>
+        <v>2.75</v>
       </c>
       <c r="P17" t="n">
-        <v>2.32</v>
+        <v>1.91</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.27</v>
+        <v>5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.34</v>
+        <v>1.6</v>
       </c>
       <c r="S17" t="n">
-        <v>3.28</v>
+        <v>2.2</v>
       </c>
       <c r="T17" t="n">
-        <v>2.67</v>
+        <v>3.75</v>
       </c>
       <c r="U17" t="n">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="V17" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="W17" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="X17" t="n">
-        <v>4.01</v>
+        <v>2.3</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.65</v>
+        <v>2.7</v>
       </c>
       <c r="Z17" t="n">
-        <v>2</v>
+        <v>1.44</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.9</v>
+        <v>4.65</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.41</v>
+        <v>1.11</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.61</v>
+        <v>2.38</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.32</v>
+        <v>1.53</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
+          <t>['45', '62', '90+3']</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>['78']</t>
-        </is>
-      </c>
       <c r="AG17" t="n">
-        <v>1.35</v>
+        <v>1.15</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45588.5</v>
@@ -2707,22 +2707,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2733,55 +2733,55 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.91</v>
+        <v>6.5</v>
       </c>
       <c r="M18" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="N18" t="n">
-        <v>4.1</v>
+        <v>1.55</v>
       </c>
       <c r="O18" t="n">
-        <v>2.75</v>
+        <v>7</v>
       </c>
       <c r="P18" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="Q18" t="n">
-        <v>5</v>
+        <v>2.25</v>
       </c>
       <c r="R18" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="S18" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="T18" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U18" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="V18" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="W18" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="X18" t="n">
-        <v>2.3</v>
+        <v>2.65</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.65</v>
+        <v>4.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AC18" t="n">
         <v>2.38</v>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>['45', '62', '90+3']</t>
+          <t>['57', '74']</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -2800,16 +2800,16 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.15</v>
+        <v>2.35</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.85</v>
+        <v>1.06</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.62</v>
+        <v>4</v>
       </c>
       <c r="AJ18" t="n">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45588.5</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.45</v>
+        <v>2.31</v>
       </c>
       <c r="M19" t="n">
-        <v>3.4</v>
+        <v>3.06</v>
       </c>
       <c r="N19" t="n">
-        <v>1.94</v>
+        <v>2.63</v>
       </c>
       <c r="O19" t="n">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="P19" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.5</v>
+        <v>3.27</v>
       </c>
       <c r="R19" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="S19" t="n">
-        <v>3.46</v>
+        <v>3.28</v>
       </c>
       <c r="T19" t="n">
-        <v>2.29</v>
+        <v>2.67</v>
       </c>
       <c r="U19" t="n">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="V19" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W19" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="X19" t="n">
-        <v>4.4</v>
+        <v>4.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.35</v>
+        <v>2.9</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.48</v>
+        <v>1.61</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2925,20 +2925,20 @@
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>['77']</t>
+          <t>['78']</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.62</v>
+        <v>1.35</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="AI19" t="n">
-        <v>2.38</v>
+        <v>1.95</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.62</v>
+        <v>2.05</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45588.5</v>
@@ -3084,35 +3084,35 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -3120,74 +3120,74 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>6.5</v>
+        <v>4.6</v>
       </c>
       <c r="M21" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="N21" t="n">
         <v>1.55</v>
       </c>
       <c r="O21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P21" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="Q21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T21" t="n">
         <v>2.25</v>
       </c>
-      <c r="R21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3.5</v>
-      </c>
       <c r="U21" t="n">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="V21" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W21" t="n">
-        <v>1.45</v>
+        <v>1.17</v>
       </c>
       <c r="X21" t="n">
-        <v>2.65</v>
+        <v>4.75</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.4</v>
+        <v>1.55</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.53</v>
+        <v>2.35</v>
       </c>
       <c r="AA21" t="n">
-        <v>4.5</v>
+        <v>2.15</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.18</v>
+        <v>1.57</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.38</v>
+        <v>1.7</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.53</v>
+        <v>1.95</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>['57', '74']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['19']</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>2.35</v>
+        <v>2.9</v>
       </c>
       <c r="AH21" t="n">
         <v>1.06</v>
@@ -3196,7 +3196,7 @@
         <v>4</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45588.5</v>
@@ -3868,25 +3868,25 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hannover 96 II</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G27" t="n">
         <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -3894,83 +3894,83 @@
         </is>
       </c>
       <c r="L27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M27" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="O27" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S27" t="n">
         <v>3.45</v>
       </c>
-      <c r="M27" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="N27" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="O27" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="P27" t="n">
+      <c r="T27" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X27" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z27" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q27" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S27" t="n">
-        <v>3</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X27" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AA27" t="n">
-        <v>2.8</v>
+        <v>2.32</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AD27" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>['72']</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>['46', '57', '90']</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ27" t="n">
         <v>2.15</v>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>['64']</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>['2', '42', '82', '88']</t>
-        </is>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1.73</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45588.58333333334</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,25 +3997,25 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Riadi Salmi</t>
+          <t>Unterhaching</t>
         </is>
       </c>
       <c r="G28" t="n">
+        <v>3</v>
+      </c>
+      <c r="H28" t="n">
         <v>1</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
       </c>
       <c r="I28" t="n">
         <v>1</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -4023,83 +4023,83 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.33</v>
+        <v>1.66</v>
       </c>
       <c r="M28" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="N28" t="n">
-        <v>8.5</v>
+        <v>4.7</v>
       </c>
       <c r="O28" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X28" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD28" t="n">
         <v>1.95</v>
       </c>
-      <c r="P28" t="n">
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>['29', '71', '84']</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>['15']</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AH28" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q28" t="n">
-        <v>10</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T28" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="X28" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z28" t="n">
+      <c r="AI28" t="n">
         <v>1.57</v>
       </c>
-      <c r="AA28" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>['45+2']</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AJ28" t="n">
-        <v>5.5</v>
+        <v>2.75</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45588.58333333334</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Riadi Salmi</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,65 +4152,65 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.1</v>
+        <v>1.33</v>
       </c>
       <c r="M29" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="N29" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="P29" t="n">
         <v>2.1</v>
       </c>
-      <c r="O29" t="n">
-        <v>3.69</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2.38</v>
-      </c>
       <c r="Q29" t="n">
-        <v>2.71</v>
+        <v>10</v>
       </c>
       <c r="R29" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="S29" t="n">
-        <v>3.25</v>
+        <v>2.4</v>
       </c>
       <c r="T29" t="n">
-        <v>2.53</v>
+        <v>3.4</v>
       </c>
       <c r="U29" t="n">
-        <v>1.51</v>
+        <v>1.28</v>
       </c>
       <c r="V29" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W29" t="n">
-        <v>1.18</v>
+        <v>1.43</v>
       </c>
       <c r="X29" t="n">
-        <v>4.2</v>
+        <v>2.68</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.6</v>
+        <v>2.35</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.25</v>
+        <v>1.57</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.5</v>
+        <v>4.1</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.47</v>
+        <v>1.14</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.27</v>
+        <v>1.36</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>['21']</t>
+          <t>['45+2']</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
@@ -4219,16 +4219,16 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.67</v>
+        <v>1.05</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.32</v>
+        <v>2.7</v>
       </c>
       <c r="AI29" t="n">
-        <v>2.25</v>
+        <v>1.25</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.8</v>
+        <v>5.5</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45588.58333333334</v>
@@ -4255,25 +4255,25 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Unterhaching</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>1</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -4281,83 +4281,83 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.66</v>
+        <v>3.1</v>
       </c>
       <c r="M30" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="N30" t="n">
-        <v>4.7</v>
+        <v>2.1</v>
       </c>
       <c r="O30" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X30" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z30" t="n">
         <v>2.25</v>
       </c>
-      <c r="P30" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X30" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AA30" t="n">
-        <v>2.95</v>
+        <v>2.5</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.95</v>
+        <v>2.27</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>['29', '71', '84']</t>
+          <t>['21']</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>['15']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.15</v>
+        <v>1.67</v>
       </c>
       <c r="AH30" t="n">
-        <v>2.1</v>
+        <v>1.32</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.57</v>
+        <v>2.25</v>
       </c>
       <c r="AJ30" t="n">
-        <v>2.75</v>
+        <v>1.8</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45588.58333333334</v>
@@ -4513,25 +4513,25 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>CD Eldense</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
         <v>1</v>
       </c>
       <c r="J32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -4539,83 +4539,83 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="M32" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N32" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="O32" t="n">
-        <v>3.45</v>
+        <v>2.95</v>
       </c>
       <c r="P32" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="R32" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="S32" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="T32" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="U32" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="V32" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="W32" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="X32" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="Z32" t="n">
         <v>1.57</v>
       </c>
       <c r="AA32" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>['11', '72']</t>
+          <t>['31']</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>['34', '45+4', '80']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AI32" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AJ32" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45588.58333333334</v>
@@ -4642,25 +4642,25 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>CD Eldense</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I33" t="n">
         <v>1</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -4668,83 +4668,83 @@
         </is>
       </c>
       <c r="L33" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="M33" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N33" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O33" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S33" t="n">
         <v>2.3</v>
       </c>
-      <c r="M33" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N33" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O33" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="P33" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S33" t="n">
-        <v>2.45</v>
-      </c>
       <c r="T33" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="U33" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="V33" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W33" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="X33" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="Z33" t="n">
         <v>1.57</v>
       </c>
       <c r="AA33" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>['31']</t>
+          <t>['11', '72']</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['34', '45+4', '80']</t>
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AJ33" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45588.58333333334</v>
@@ -4771,109 +4771,109 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Hannover 96 II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="G34" t="n">
         <v>1</v>
       </c>
       <c r="H34" t="n">
+        <v>4</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="M34" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N34" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="O34" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S34" t="n">
         <v>3</v>
       </c>
-      <c r="I34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L34" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="M34" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="N34" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="O34" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="P34" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S34" t="n">
-        <v>3.45</v>
-      </c>
       <c r="T34" t="n">
-        <v>2.37</v>
+        <v>2.55</v>
       </c>
       <c r="U34" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X34" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC34" t="n">
         <v>1.57</v>
       </c>
-      <c r="V34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X34" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AD34" t="n">
-        <v>2.43</v>
+        <v>2.15</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>['72']</t>
+          <t>['64']</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>['46', '57', '90']</t>
+          <t>['2', '42', '82', '88']</t>
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.35</v>
+        <v>1.77</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.65</v>
+        <v>1.3</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.8</v>
+        <v>2.35</v>
       </c>
       <c r="AJ34" t="n">
-        <v>2.15</v>
+        <v>1.73</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45588.58333333334</v>
@@ -4900,69 +4900,69 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G35" t="n">
+        <v>2</v>
+      </c>
+      <c r="H35" t="n">
+        <v>3</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
         <v>1</v>
       </c>
-      <c r="H35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.83</v>
+        <v>2.9</v>
       </c>
       <c r="M35" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="N35" t="n">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="O35" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="P35" t="n">
         <v>2.05</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.75</v>
+        <v>3</v>
       </c>
       <c r="R35" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
         <v>2.2</v>
@@ -4971,38 +4971,38 @@
         <v>1.65</v>
       </c>
       <c r="AA35" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>['57', '87']</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>['22', '46', '69']</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AJ35" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>['74']</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>3.1</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45588.60416666666</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,25 +5029,25 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Chippa United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -5055,83 +5055,83 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.63</v>
+        <v>4.3</v>
       </c>
       <c r="M36" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="N36" t="n">
-        <v>2.5</v>
+        <v>1.87</v>
       </c>
       <c r="O36" t="n">
-        <v>3.25</v>
+        <v>5</v>
       </c>
       <c r="P36" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.2</v>
+        <v>2.35</v>
       </c>
       <c r="R36" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="S36" t="n">
-        <v>2.68</v>
+        <v>2.4</v>
       </c>
       <c r="T36" t="n">
-        <v>3.26</v>
+        <v>3.3</v>
       </c>
       <c r="U36" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="V36" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="W36" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="X36" t="n">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="Y36" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AA36" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.87</v>
+        <v>2.25</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.87</v>
+        <v>1.6</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>['10']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>['61']</t>
+          <t>['31', '43']</t>
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.51</v>
+        <v>2.1</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.34</v>
+        <v>1.11</v>
       </c>
       <c r="AI36" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45588.60416666666</v>
@@ -5158,22 +5158,22 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Nîmes</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -5184,65 +5184,65 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="M37" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="N37" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="O37" t="n">
         <v>3.1</v>
       </c>
       <c r="P37" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="R37" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="S37" t="n">
-        <v>2.5</v>
+        <v>2.81</v>
       </c>
       <c r="T37" t="n">
-        <v>3.27</v>
+        <v>3.08</v>
       </c>
       <c r="U37" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W37" t="n">
         <v>1.3</v>
       </c>
-      <c r="V37" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.36</v>
-      </c>
       <c r="X37" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AA37" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>['26', '81']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
@@ -5251,16 +5251,16 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.62</v>
+        <v>1.47</v>
       </c>
       <c r="AI37" t="n">
         <v>1.91</v>
       </c>
       <c r="AJ37" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45588.60416666666</v>
@@ -5287,22 +5287,22 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G38" t="n">
         <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -5313,83 +5313,83 @@
         </is>
       </c>
       <c r="L38" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="M38" t="n">
+        <v>3</v>
+      </c>
+      <c r="N38" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O38" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P38" t="n">
         <v>2.05</v>
       </c>
-      <c r="M38" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="N38" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O38" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P38" t="n">
-        <v>2</v>
-      </c>
       <c r="Q38" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X38" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA38" t="n">
         <v>4</v>
       </c>
-      <c r="R38" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="S38" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="T38" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X38" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AB38" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>['90+3']</t>
+          <t>['10']</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['61']</t>
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.25</v>
+        <v>1.51</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.68</v>
+        <v>1.34</v>
       </c>
       <c r="AI38" t="n">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="AJ38" t="n">
-        <v>2.75</v>
+        <v>1.91</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45588.60416666666</v>
@@ -5416,25 +5416,25 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Nîmes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="G39" t="n">
         <v>2</v>
       </c>
       <c r="H39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -5442,83 +5442,83 @@
         </is>
       </c>
       <c r="L39" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M39" t="n">
         <v>2.9</v>
       </c>
-      <c r="M39" t="n">
-        <v>3</v>
-      </c>
       <c r="N39" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="O39" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q39" t="n">
         <v>3.5</v>
       </c>
-      <c r="P39" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>3</v>
-      </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>['57', '87']</t>
+          <t>['26', '81']</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>['22', '46', '69']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI39" t="n">
-        <v>2.38</v>
+        <v>1.91</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45588.60416666666</v>
@@ -5545,16 +5545,16 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -5571,83 +5571,83 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.45</v>
+        <v>1.83</v>
       </c>
       <c r="M40" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N40" t="n">
+        <v>4</v>
+      </c>
+      <c r="O40" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P40" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S40" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X40" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>['74']</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG40" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ40" t="n">
         <v>3.1</v>
-      </c>
-      <c r="N40" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="O40" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P40" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S40" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="T40" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X40" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG40" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>2.2</v>
       </c>
       <c r="AK40" s="3" t="n">
         <v>45588.60416666666</v>
@@ -5674,22 +5674,22 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -5700,55 +5700,55 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.9</v>
+        <v>1.75</v>
       </c>
       <c r="M41" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="N41" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="O41" t="n">
-        <v>3.5</v>
+        <v>2.38</v>
       </c>
       <c r="P41" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q41" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="R41" t="n">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="S41" t="n">
-        <v>2.5</v>
+        <v>2.83</v>
       </c>
       <c r="T41" t="n">
-        <v>3.18</v>
+        <v>2.99</v>
       </c>
       <c r="U41" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V41" t="n">
         <v>1.05</v>
       </c>
       <c r="W41" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="X41" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AA41" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC41" t="n">
         <v>1.87</v>
@@ -5758,25 +5758,25 @@
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>['24', '30']</t>
+          <t>['90+4']</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['72']</t>
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.47</v>
+        <v>1.16</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.42</v>
+        <v>1.96</v>
       </c>
       <c r="AI41" t="n">
-        <v>2.38</v>
+        <v>1.5</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45588.60416666666</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,25 +5803,25 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Chippa United</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5829,28 +5829,28 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>4.3</v>
+        <v>2.05</v>
       </c>
       <c r="M42" t="n">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="N42" t="n">
-        <v>1.87</v>
+        <v>3.6</v>
       </c>
       <c r="O42" t="n">
-        <v>5</v>
+        <v>2.75</v>
       </c>
       <c r="P42" t="n">
         <v>2</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.35</v>
+        <v>4</v>
       </c>
       <c r="R42" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="S42" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="T42" t="n">
         <v>3.3</v>
@@ -5859,53 +5859,53 @@
         <v>1.28</v>
       </c>
       <c r="V42" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W42" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="X42" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="Y42" t="n">
         <v>2.35</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AA42" t="n">
         <v>4.5</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
+          <t>['90+3']</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF42" t="inlineStr">
-        <is>
-          <t>['31', '43']</t>
-        </is>
-      </c>
       <c r="AG42" t="n">
-        <v>2.1</v>
+        <v>1.25</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.11</v>
+        <v>1.68</v>
       </c>
       <c r="AI42" t="n">
-        <v>3.1</v>
+        <v>1.73</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1.57</v>
+        <v>2.75</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45588.60416666666</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,22 +5932,22 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Real Kings</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G43" t="n">
         <v>2</v>
       </c>
       <c r="H43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -5958,83 +5958,83 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.25</v>
+        <v>2.9</v>
       </c>
       <c r="M43" t="n">
-        <v>4.47</v>
+        <v>3</v>
       </c>
       <c r="N43" t="n">
-        <v>7.7</v>
+        <v>2.3</v>
       </c>
       <c r="O43" t="n">
-        <v>1.83</v>
+        <v>3.5</v>
       </c>
       <c r="P43" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Q43" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="R43" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="S43" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="T43" t="n">
-        <v>2.75</v>
+        <v>3.18</v>
       </c>
       <c r="U43" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="V43" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W43" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="X43" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.97</v>
+        <v>2.2</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="AA43" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.5</v>
+        <v>1.87</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.5</v>
+        <v>1.87</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>['6', '85']</t>
+          <t>['24', '30']</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>['90+2']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.03</v>
+        <v>1.47</v>
       </c>
       <c r="AH43" t="n">
-        <v>3</v>
+        <v>1.42</v>
       </c>
       <c r="AI43" t="n">
-        <v>1.25</v>
+        <v>2.38</v>
       </c>
       <c r="AJ43" t="n">
-        <v>4.75</v>
+        <v>1.8</v>
       </c>
       <c r="AK43" s="3" t="n">
         <v>45588.60416666666</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,22 +6061,22 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Real Kings</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H44" t="n">
         <v>1</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -6087,83 +6087,83 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="M44" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="N44" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="O44" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P44" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>8</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S44" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X44" t="n">
         <v>3.4</v>
       </c>
-      <c r="N44" t="n">
-        <v>4</v>
-      </c>
-      <c r="O44" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="P44" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R44" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S44" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="T44" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="U44" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V44" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W44" t="n">
+      <c r="Y44" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB44" t="n">
         <v>1.3</v>
       </c>
-      <c r="X44" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AC44" t="n">
-        <v>1.87</v>
+        <v>2.5</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.87</v>
+        <v>1.5</v>
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>['90+4']</t>
+          <t>['6', '85']</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>['72']</t>
+          <t>['90+2']</t>
         </is>
       </c>
       <c r="AG44" t="n">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.96</v>
+        <v>3</v>
       </c>
       <c r="AI44" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AJ44" t="n">
-        <v>3</v>
+        <v>4.75</v>
       </c>
       <c r="AK44" s="3" t="n">
         <v>45588.60416666666</v>
@@ -6190,22 +6190,22 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -6216,65 +6216,65 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.64</v>
+        <v>3</v>
       </c>
       <c r="M45" t="n">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="N45" t="n">
-        <v>5.6</v>
+        <v>2.42</v>
       </c>
       <c r="O45" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="P45" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Q45" t="n">
-        <v>6</v>
+        <v>3.1</v>
       </c>
       <c r="R45" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S45" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="T45" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U45" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W45" t="n">
         <v>1.36</v>
       </c>
-      <c r="V45" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W45" t="n">
-        <v>1.33</v>
-      </c>
       <c r="X45" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="Y45" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AA45" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC45" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>['13']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF45" t="inlineStr">
@@ -6283,16 +6283,16 @@
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>1.16</v>
+        <v>1.53</v>
       </c>
       <c r="AH45" t="n">
-        <v>2.3</v>
+        <v>1.47</v>
       </c>
       <c r="AI45" t="n">
-        <v>1.4</v>
+        <v>2.25</v>
       </c>
       <c r="AJ45" t="n">
-        <v>3.25</v>
+        <v>1.8</v>
       </c>
       <c r="AK45" s="3" t="n">
         <v>45588.65625</v>
@@ -6319,22 +6319,22 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="M46" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="N46" t="n">
-        <v>2.42</v>
+        <v>2.85</v>
       </c>
       <c r="O46" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P46" t="n">
         <v>2.05</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="R46" t="n">
         <v>1.44</v>
@@ -6375,7 +6375,7 @@
         <v>1.33</v>
       </c>
       <c r="V46" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="W46" t="n">
         <v>1.36</v>
@@ -6384,10 +6384,10 @@
         <v>3.2</v>
       </c>
       <c r="Y46" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AA46" t="n">
         <v>3.75</v>
@@ -6403,25 +6403,25 @@
       </c>
       <c r="AE46" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45']</t>
         </is>
       </c>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['77']</t>
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="AI46" t="n">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="AJ46" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AK46" s="3" t="n">
         <v>45588.65625</v>
@@ -6448,19 +6448,19 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G47" t="n">
         <v>1</v>
       </c>
       <c r="H47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
         <v>1</v>
@@ -6474,83 +6474,83 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.6</v>
+        <v>1.64</v>
       </c>
       <c r="M47" t="n">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="N47" t="n">
-        <v>2.85</v>
+        <v>5.6</v>
       </c>
       <c r="O47" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="P47" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="R47" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S47" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="T47" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="U47" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W47" t="n">
         <v>1.33</v>
       </c>
-      <c r="V47" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W47" t="n">
-        <v>1.36</v>
-      </c>
       <c r="X47" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="Y47" t="n">
         <v>2.05</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="AA47" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>['45']</t>
+          <t>['13']</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>['77']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.47</v>
+        <v>1.16</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.55</v>
+        <v>2.3</v>
       </c>
       <c r="AI47" t="n">
-        <v>1.83</v>
+        <v>1.4</v>
       </c>
       <c r="AJ47" t="n">
-        <v>2.2</v>
+        <v>3.25</v>
       </c>
       <c r="AK47" s="3" t="n">
         <v>45588.65625</v>
@@ -6706,25 +6706,25 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
         <v>1</v>
       </c>
-      <c r="I49" t="n">
-        <v>0</v>
-      </c>
       <c r="J49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -6732,83 +6732,83 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>3.55</v>
+        <v>1.09</v>
       </c>
       <c r="M49" t="n">
-        <v>3.9</v>
+        <v>11</v>
       </c>
       <c r="N49" t="n">
-        <v>1.96</v>
+        <v>23</v>
       </c>
       <c r="O49" t="n">
-        <v>4</v>
+        <v>1.33</v>
       </c>
       <c r="P49" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.38</v>
+        <v>19</v>
       </c>
       <c r="R49" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="S49" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="T49" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="U49" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="V49" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W49" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X49" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>['3', '58', '64', '68', '88']</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG49" t="n">
         <v>1.02</v>
       </c>
-      <c r="W49" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X49" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF49" t="inlineStr">
-        <is>
-          <t>['27']</t>
-        </is>
-      </c>
-      <c r="AG49" t="n">
-        <v>1.98</v>
-      </c>
       <c r="AH49" t="n">
-        <v>1.29</v>
+        <v>8</v>
       </c>
       <c r="AI49" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="AJ49" t="n">
-        <v>1.53</v>
+        <v>7</v>
       </c>
       <c r="AK49" s="3" t="n">
         <v>45588.66666666666</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,25 +6835,25 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>FC Cartagena</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -6861,83 +6861,83 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>4.3</v>
+        <v>3.55</v>
       </c>
       <c r="M50" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="N50" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="O50" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="P50" t="n">
-        <v>1.93</v>
+        <v>2.5</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="R50" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S50" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V50" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W50" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X50" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>['27']</t>
+        </is>
+      </c>
+      <c r="AG50" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AJ50" t="n">
         <v>1.53</v>
-      </c>
-      <c r="S50" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="T50" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U50" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V50" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W50" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="X50" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG50" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI50" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>1.7</v>
       </c>
       <c r="AK50" s="3" t="n">
         <v>45588.66666666666</v>
@@ -6964,109 +6964,109 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G51" t="n">
+        <v>4</v>
+      </c>
+      <c r="H51" t="n">
         <v>1</v>
       </c>
-      <c r="H51" t="n">
+      <c r="I51" t="n">
         <v>3</v>
       </c>
-      <c r="I51" t="n">
+      <c r="J51" t="n">
         <v>1</v>
       </c>
-      <c r="J51" t="n">
-        <v>0</v>
-      </c>
       <c r="K51" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.45</v>
+        <v>2.44</v>
       </c>
       <c r="M51" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="N51" t="n">
-        <v>7.4</v>
+        <v>2.65</v>
       </c>
       <c r="O51" t="n">
-        <v>2.05</v>
+        <v>2.63</v>
       </c>
       <c r="P51" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="Q51" t="n">
-        <v>6.5</v>
+        <v>3.2</v>
       </c>
       <c r="R51" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S51" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W51" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X51" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC51" t="n">
         <v>1.36</v>
       </c>
-      <c r="S51" t="n">
+      <c r="AD51" t="n">
         <v>3</v>
       </c>
-      <c r="T51" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U51" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V51" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W51" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X51" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AE51" t="inlineStr">
         <is>
-          <t>['8']</t>
+          <t>['1', '36', '45', '56']</t>
         </is>
       </c>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>['61', '74', '89']</t>
+          <t>['18']</t>
         </is>
       </c>
       <c r="AG51" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="AH51" t="n">
-        <v>2.77</v>
+        <v>1.63</v>
       </c>
       <c r="AI51" t="n">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="AJ51" t="n">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="AK51" s="3" t="n">
         <v>45588.66666666666</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,22 +7093,22 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -7119,65 +7119,65 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.09</v>
+        <v>2.16</v>
       </c>
       <c r="M52" t="n">
-        <v>11</v>
+        <v>3.55</v>
       </c>
       <c r="N52" t="n">
-        <v>23</v>
+        <v>3.55</v>
       </c>
       <c r="O52" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P52" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>4</v>
+      </c>
+      <c r="R52" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S52" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V52" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W52" t="n">
         <v>1.33</v>
       </c>
-      <c r="P52" t="n">
+      <c r="X52" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AA52" t="n">
         <v>3.6</v>
       </c>
-      <c r="Q52" t="n">
-        <v>19</v>
-      </c>
-      <c r="R52" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S52" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T52" t="n">
+      <c r="AB52" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC52" t="n">
         <v>1.83</v>
       </c>
-      <c r="U52" t="n">
+      <c r="AD52" t="n">
         <v>1.83</v>
       </c>
-      <c r="V52" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W52" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X52" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>['3', '58', '64', '68', '88']</t>
+          <t>['80']</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
@@ -7186,16 +7186,16 @@
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>1.02</v>
+        <v>1.32</v>
       </c>
       <c r="AH52" t="n">
-        <v>8</v>
+        <v>1.75</v>
       </c>
       <c r="AI52" t="n">
-        <v>1.1</v>
+        <v>1.67</v>
       </c>
       <c r="AJ52" t="n">
-        <v>7</v>
+        <v>2.4</v>
       </c>
       <c r="AK52" s="3" t="n">
         <v>45588.66666666666</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,19 +7222,19 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>FC Cartagena</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
@@ -7248,31 +7248,31 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.07</v>
+        <v>4.3</v>
       </c>
       <c r="M53" t="n">
-        <v>2.8</v>
+        <v>3.35</v>
       </c>
       <c r="N53" t="n">
-        <v>3.04</v>
+        <v>1.93</v>
       </c>
       <c r="O53" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="P53" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="Q53" t="n">
-        <v>4.33</v>
+        <v>2.6</v>
       </c>
       <c r="R53" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="S53" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="T53" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U53" t="n">
         <v>1.25</v>
@@ -7281,25 +7281,25 @@
         <v>1.09</v>
       </c>
       <c r="W53" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="X53" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="Y53" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AA53" t="n">
         <v>4.75</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AC53" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD53" t="n">
         <v>1.62</v>
@@ -7311,20 +7311,20 @@
       </c>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>['90+4']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG53" t="n">
-        <v>1.33</v>
+        <v>1.83</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="AI53" t="n">
-        <v>1.8</v>
+        <v>2.75</v>
       </c>
       <c r="AJ53" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="AK53" s="3" t="n">
         <v>45588.66666666666</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,20 +7351,20 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
         <v>1</v>
       </c>
-      <c r="H54" t="n">
-        <v>0</v>
-      </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
@@ -7377,83 +7377,83 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.16</v>
+        <v>2.07</v>
       </c>
       <c r="M54" t="n">
-        <v>3.55</v>
+        <v>2.8</v>
       </c>
       <c r="N54" t="n">
-        <v>3.55</v>
+        <v>3.04</v>
       </c>
       <c r="O54" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="P54" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="Q54" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="R54" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="S54" t="n">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="T54" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="U54" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="V54" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="W54" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X54" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>['90+4']</t>
+        </is>
+      </c>
+      <c r="AG54" t="n">
         <v>1.33</v>
       </c>
-      <c r="X54" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE54" t="inlineStr">
-        <is>
-          <t>['80']</t>
-        </is>
-      </c>
-      <c r="AF54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG54" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AH54" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AI54" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AJ54" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AK54" s="3" t="n">
         <v>45588.66666666666</v>
@@ -7609,25 +7609,25 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
         <v>1</v>
       </c>
       <c r="I56" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -7635,83 +7635,83 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>2.44</v>
+        <v>6.4</v>
       </c>
       <c r="M56" t="n">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="N56" t="n">
-        <v>2.65</v>
+        <v>1.47</v>
       </c>
       <c r="O56" t="n">
-        <v>2.63</v>
+        <v>6.5</v>
       </c>
       <c r="P56" t="n">
         <v>2.6</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.2</v>
+        <v>1.83</v>
       </c>
       <c r="R56" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="S56" t="n">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="T56" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="U56" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="V56" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W56" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="X56" t="n">
-        <v>6.8</v>
+        <v>5.2</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="Z56" t="n">
-        <v>2.32</v>
+        <v>2.43</v>
       </c>
       <c r="AA56" t="n">
-        <v>2.2</v>
+        <v>2.47</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AC56" t="n">
-        <v>1.36</v>
+        <v>1.8</v>
       </c>
       <c r="AD56" t="n">
-        <v>3</v>
+        <v>1.95</v>
       </c>
       <c r="AE56" t="inlineStr">
         <is>
-          <t>['1', '36', '45', '56']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>['18']</t>
+          <t>['90+3']</t>
         </is>
       </c>
       <c r="AG56" t="n">
-        <v>1.5</v>
+        <v>3.05</v>
       </c>
       <c r="AH56" t="n">
-        <v>1.63</v>
+        <v>1.08</v>
       </c>
       <c r="AI56" t="n">
-        <v>1.67</v>
+        <v>3.75</v>
       </c>
       <c r="AJ56" t="n">
-        <v>2.1</v>
+        <v>1.29</v>
       </c>
       <c r="AK56" s="3" t="n">
         <v>45588.66666666666</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,109 +7738,109 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="M57" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N57" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O57" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P57" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>4</v>
+      </c>
+      <c r="R57" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S57" t="n">
         <v>3</v>
       </c>
-      <c r="I57" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" t="n">
-        <v>2</v>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L57" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="M57" t="n">
+      <c r="T57" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V57" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W57" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X57" t="n">
         <v>3.95</v>
       </c>
-      <c r="N57" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O57" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="P57" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>5</v>
-      </c>
-      <c r="R57" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S57" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T57" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U57" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V57" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W57" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X57" t="n">
-        <v>4.85</v>
-      </c>
       <c r="Y57" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC57" t="n">
         <v>1.6</v>
       </c>
-      <c r="Z57" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AB57" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC57" t="n">
+      <c r="AD57" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>['73', '87']</t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG57" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI57" t="n">
         <v>1.67</v>
       </c>
-      <c r="AD57" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE57" t="inlineStr">
-        <is>
-          <t>['66']</t>
-        </is>
-      </c>
-      <c r="AF57" t="inlineStr">
-        <is>
-          <t>['12', '33', '90+2']</t>
-        </is>
-      </c>
-      <c r="AG57" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AH57" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AI57" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AJ57" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AK57" s="3" t="n">
         <v>45588.66666666666</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,109 +7867,109 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G58" t="n">
+        <v>1</v>
+      </c>
+      <c r="H58" t="n">
+        <v>3</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="n">
         <v>2</v>
       </c>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" t="n">
-        <v>0</v>
-      </c>
       <c r="K58" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="M58" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="N58" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="O58" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P58" t="n">
         <v>2.4</v>
       </c>
-      <c r="P58" t="n">
-        <v>2.2</v>
-      </c>
       <c r="Q58" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R58" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="S58" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V58" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W58" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X58" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>['66']</t>
+        </is>
+      </c>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>['12', '33', '90+2']</t>
+        </is>
+      </c>
+      <c r="AG58" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AH58" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AI58" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AJ58" t="n">
         <v>3</v>
-      </c>
-      <c r="T58" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U58" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V58" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W58" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X58" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="Y58" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z58" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA58" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AB58" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC58" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AD58" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AE58" t="inlineStr">
-        <is>
-          <t>['73', '87']</t>
-        </is>
-      </c>
-      <c r="AF58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG58" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH58" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AI58" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AJ58" t="n">
-        <v>2.5</v>
       </c>
       <c r="AK58" s="3" t="n">
         <v>45588.66666666666</v>
@@ -7996,23 +7996,23 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H59" t="n">
+        <v>3</v>
+      </c>
+      <c r="I59" t="n">
         <v>1</v>
       </c>
-      <c r="I59" t="n">
-        <v>0</v>
-      </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
@@ -8022,83 +8022,83 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>6.4</v>
+        <v>1.45</v>
       </c>
       <c r="M59" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="N59" t="n">
-        <v>1.47</v>
+        <v>7.4</v>
       </c>
       <c r="O59" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="P59" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q59" t="n">
         <v>6.5</v>
       </c>
-      <c r="P59" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>1.83</v>
-      </c>
       <c r="R59" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="S59" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="T59" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="U59" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="V59" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W59" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="X59" t="n">
-        <v>5.2</v>
+        <v>3.7</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.59</v>
+        <v>1.86</v>
       </c>
       <c r="Z59" t="n">
-        <v>2.43</v>
+        <v>1.95</v>
       </c>
       <c r="AA59" t="n">
-        <v>2.47</v>
+        <v>3.35</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.57</v>
+        <v>1.35</v>
       </c>
       <c r="AC59" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AD59" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AE59" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['8']</t>
         </is>
       </c>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>['90+3']</t>
+          <t>['61', '74', '89']</t>
         </is>
       </c>
       <c r="AG59" t="n">
-        <v>3.05</v>
+        <v>1.1</v>
       </c>
       <c r="AH59" t="n">
-        <v>1.08</v>
+        <v>2.77</v>
       </c>
       <c r="AI59" t="n">
-        <v>3.75</v>
+        <v>1.33</v>
       </c>
       <c r="AJ59" t="n">
-        <v>1.29</v>
+        <v>3.6</v>
       </c>
       <c r="AK59" s="3" t="n">
         <v>45588.66666666666</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,25 +8512,25 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="G63" t="n">
         <v>2</v>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -8538,83 +8538,83 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.52</v>
+        <v>1.57</v>
       </c>
       <c r="M63" t="n">
-        <v>2.9</v>
+        <v>3.52</v>
       </c>
       <c r="N63" t="n">
-        <v>2.28</v>
+        <v>4.31</v>
       </c>
       <c r="O63" t="n">
-        <v>3.25</v>
+        <v>2</v>
       </c>
       <c r="P63" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>5</v>
+      </c>
+      <c r="R63" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S63" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V63" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W63" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X63" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD63" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q63" t="n">
-        <v>3</v>
-      </c>
-      <c r="R63" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S63" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T63" t="n">
-        <v>3</v>
-      </c>
-      <c r="U63" t="n">
+      <c r="AE63" t="inlineStr">
+        <is>
+          <t>['21', '64']</t>
+        </is>
+      </c>
+      <c r="AF63" t="inlineStr">
+        <is>
+          <t>['14', '45+6']</t>
+        </is>
+      </c>
+      <c r="AG63" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AH63" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AI63" t="n">
         <v>1.36</v>
       </c>
-      <c r="V63" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W63" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X63" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="Y63" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Z63" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AA63" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AB63" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AC63" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD63" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE63" t="inlineStr">
-        <is>
-          <t>['47', '90+2']</t>
-        </is>
-      </c>
-      <c r="AF63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG63" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AH63" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI63" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AJ63" t="n">
-        <v>1.83</v>
+        <v>3.1</v>
       </c>
       <c r="AK63" s="3" t="n">
         <v>45588.85416666666</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,25 +8641,25 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G64" t="n">
         <v>2</v>
       </c>
       <c r="H64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -8667,83 +8667,83 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.57</v>
+        <v>2.52</v>
       </c>
       <c r="M64" t="n">
-        <v>3.52</v>
+        <v>2.9</v>
       </c>
       <c r="N64" t="n">
-        <v>4.31</v>
+        <v>2.28</v>
       </c>
       <c r="O64" t="n">
-        <v>2</v>
+        <v>3.25</v>
       </c>
       <c r="P64" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="Q64" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R64" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="S64" t="n">
-        <v>3.5</v>
+        <v>2.63</v>
       </c>
       <c r="T64" t="n">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="U64" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="V64" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W64" t="n">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="X64" t="n">
-        <v>4.8</v>
+        <v>3.35</v>
       </c>
       <c r="Y64" t="n">
-        <v>1.82</v>
+        <v>1.98</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.92</v>
+        <v>1.78</v>
       </c>
       <c r="AA64" t="n">
-        <v>2.25</v>
+        <v>3.15</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.57</v>
+        <v>1.32</v>
       </c>
       <c r="AC64" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AD64" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AE64" t="inlineStr">
         <is>
-          <t>['21', '64']</t>
+          <t>['47', '90+2']</t>
         </is>
       </c>
       <c r="AF64" t="inlineStr">
         <is>
-          <t>['14', '45+6']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG64" t="n">
-        <v>1.13</v>
+        <v>1.42</v>
       </c>
       <c r="AH64" t="n">
-        <v>2.26</v>
+        <v>1.36</v>
       </c>
       <c r="AI64" t="n">
-        <v>1.36</v>
+        <v>2.2</v>
       </c>
       <c r="AJ64" t="n">
-        <v>3.1</v>
+        <v>1.83</v>
       </c>
       <c r="AK64" s="3" t="n">
         <v>45588.85416666666</v>
